--- a/Team-Data/2020-21/1-14-2020-21.xlsx
+++ b/Team-Data/2020-21/1-14-2020-21.xlsx
@@ -806,16 +806,16 @@
         <v>4.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
         <v>17</v>
@@ -824,10 +824,10 @@
         <v>22</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
         <v>7</v>
@@ -836,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -857,16 +857,16 @@
         <v>2</v>
       </c>
       <c r="AU2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>26</v>
       </c>
       <c r="AX2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY2" t="n">
         <v>21</v>
@@ -875,10 +875,10 @@
         <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
         <v>6</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -988,10 +988,10 @@
         <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF3" t="n">
         <v>1</v>
@@ -1006,13 +1006,13 @@
         <v>7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK3" t="n">
         <v>6</v>
       </c>
       <c r="AL3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM3" t="n">
         <v>26</v>
@@ -1024,22 +1024,22 @@
         <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
         <v>4</v>
       </c>
       <c r="AS3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV3" t="n">
         <v>24</v>
@@ -1054,7 +1054,7 @@
         <v>18</v>
       </c>
       <c r="AZ3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
         <v>18</v>
@@ -1063,7 +1063,7 @@
         <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -1173,16 +1173,16 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
         <v>6</v>
@@ -1203,7 +1203,7 @@
         <v>4</v>
       </c>
       <c r="AO4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP4" t="n">
         <v>9</v>
@@ -1212,10 +1212,10 @@
         <v>8</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
         <v>8</v>
@@ -1242,11 +1242,11 @@
         <v>10</v>
       </c>
       <c r="BB4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC4" t="n">
         <v>3</v>
       </c>
-      <c r="BC4" t="n">
-        <v>4</v>
-      </c>
       <c r="BD4" t="n">
         <v>10</v>
       </c>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -1274,94 +1274,94 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>39.1</v>
+        <v>38.8</v>
       </c>
       <c r="J5" t="n">
         <v>87.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.445</v>
+        <v>0.442</v>
       </c>
       <c r="L5" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="M5" t="n">
         <v>35.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.363</v>
+        <v>0.358</v>
       </c>
       <c r="O5" t="n">
-        <v>16.1</v>
+        <v>16.7</v>
       </c>
       <c r="P5" t="n">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0.733</v>
       </c>
       <c r="R5" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="S5" t="n">
-        <v>33.6</v>
+        <v>33.9</v>
       </c>
       <c r="T5" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>28.7</v>
       </c>
       <c r="V5" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="W5" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y5" t="n">
         <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="AB5" t="n">
         <v>107.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>11</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
         <v>17</v>
@@ -1373,31 +1373,31 @@
         <v>20</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AL5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
         <v>14</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ5" t="n">
         <v>25</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
@@ -1406,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW5" t="n">
         <v>5</v>
@@ -1415,13 +1415,13 @@
         <v>10</v>
       </c>
       <c r="AY5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA5" t="n">
         <v>20</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>21</v>
       </c>
       <c r="BB5" t="n">
         <v>24</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -1534,43 +1534,43 @@
         <v>-5</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
         <v>23</v>
       </c>
       <c r="AF6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH6" t="n">
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ6" t="n">
         <v>19</v>
       </c>
       <c r="AK6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM6" t="n">
         <v>15</v>
       </c>
       <c r="AN6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
         <v>3</v>
@@ -1579,34 +1579,34 @@
         <v>25</v>
       </c>
       <c r="AS6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
         <v>30</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>26</v>
       </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>27</v>
-      </c>
       <c r="BA6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC6" t="n">
         <v>24</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -1716,19 +1716,19 @@
         <v>-5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
         <v>26</v>
@@ -1767,7 +1767,7 @@
         <v>22</v>
       </c>
       <c r="AU7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV7" t="n">
         <v>27</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
         <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1907,10 +1907,10 @@
         <v>3</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI8" t="n">
         <v>26</v>
@@ -1931,31 +1931,31 @@
         <v>22</v>
       </c>
       <c r="AO8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP8" t="n">
         <v>6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
         <v>24</v>
       </c>
       <c r="AS8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
         <v>16</v>
       </c>
       <c r="AU8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV8" t="n">
         <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX8" t="n">
         <v>18</v>
@@ -1967,13 +1967,13 @@
         <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB8" t="n">
         <v>21</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -2002,94 +2002,94 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="H9" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I9" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="J9" t="n">
-        <v>87.8</v>
+        <v>87.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.491</v>
+        <v>0.494</v>
       </c>
       <c r="L9" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="M9" t="n">
-        <v>34.1</v>
+        <v>33.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.377</v>
+        <v>0.384</v>
       </c>
       <c r="O9" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="P9" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.739</v>
+        <v>0.735</v>
       </c>
       <c r="R9" t="n">
         <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>32.4</v>
+        <v>31.7</v>
       </c>
       <c r="T9" t="n">
-        <v>42.4</v>
+        <v>41.7</v>
       </c>
       <c r="U9" t="n">
-        <v>27.3</v>
+        <v>27.2</v>
       </c>
       <c r="V9" t="n">
         <v>14.8</v>
       </c>
       <c r="W9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="X9" t="n">
         <v>4.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>116.3</v>
+        <v>116.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
         <v>2</v>
@@ -2101,40 +2101,40 @@
         <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AM9" t="n">
         <v>19</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO9" t="n">
         <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR9" t="n">
         <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW9" t="n">
         <v>9</v>
@@ -2146,16 +2146,16 @@
         <v>7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -2229,16 +2229,16 @@
         <v>11.3</v>
       </c>
       <c r="S10" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T10" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U10" t="n">
         <v>23.7</v>
       </c>
       <c r="V10" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
         <v>8.4</v>
@@ -2262,10 +2262,10 @@
         <v>-6.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF10" t="n">
         <v>30</v>
@@ -2289,10 +2289,10 @@
         <v>16</v>
       </c>
       <c r="AM10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO10" t="n">
         <v>9</v>
@@ -2310,22 +2310,22 @@
         <v>27</v>
       </c>
       <c r="AT10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ10" t="n">
         <v>12</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -2366,130 +2366,130 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="J11" t="n">
-        <v>89.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0.439</v>
+        <v>0.436</v>
       </c>
       <c r="L11" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="M11" t="n">
-        <v>37.8</v>
+        <v>38.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O11" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="P11" t="n">
         <v>24.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.788</v>
+        <v>0.795</v>
       </c>
       <c r="R11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="S11" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="T11" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U11" t="n">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="V11" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="W11" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X11" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="Y11" t="n">
         <v>5.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>111.3</v>
+        <v>112</v>
       </c>
       <c r="AC11" t="n">
-        <v>-4</v>
+        <v>-3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>11</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP11" t="n">
         <v>5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR11" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT11" t="n">
         <v>17</v>
@@ -2498,25 +2498,25 @@
         <v>14</v>
       </c>
       <c r="AV11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
         <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC11" t="n">
         <v>22</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -2548,100 +2548,100 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
         <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="H12" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I12" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="J12" t="n">
         <v>86.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L12" t="n">
         <v>13.1</v>
       </c>
       <c r="M12" t="n">
-        <v>38.2</v>
+        <v>38.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.338</v>
       </c>
       <c r="O12" t="n">
-        <v>17.6</v>
+        <v>18.2</v>
       </c>
       <c r="P12" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.752</v>
+        <v>0.763</v>
       </c>
       <c r="R12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="S12" t="n">
-        <v>34.7</v>
+        <v>34.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43</v>
+        <v>42.3</v>
       </c>
       <c r="U12" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V12" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="W12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="X12" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>111.1</v>
+        <v>111.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.3</v>
+        <v>-1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AH12" t="n">
         <v>4</v>
       </c>
       <c r="AI12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ12" t="n">
         <v>23</v>
@@ -2653,34 +2653,34 @@
         <v>13</v>
       </c>
       <c r="AM12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP12" t="n">
         <v>8</v>
       </c>
-      <c r="AN12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>7</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AW12" t="n">
         <v>14</v>
@@ -2689,19 +2689,19 @@
         <v>2</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>15</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -2730,103 +2730,103 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.667</v>
+        <v>0.636</v>
       </c>
       <c r="H13" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="J13" t="n">
-        <v>90.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0.484</v>
       </c>
       <c r="L13" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="M13" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.357</v>
+        <v>0.361</v>
       </c>
       <c r="O13" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="P13" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.751</v>
+        <v>0.749</v>
       </c>
       <c r="R13" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="T13" t="n">
-        <v>43.1</v>
+        <v>42.5</v>
       </c>
       <c r="U13" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="V13" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W13" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X13" t="n">
         <v>5.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.3</v>
+        <v>22.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>114.3</v>
+        <v>114.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE13" t="n">
         <v>5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>3</v>
       </c>
       <c r="AF13" t="n">
         <v>3</v>
       </c>
       <c r="AG13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI13" t="n">
         <v>3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK13" t="n">
         <v>5</v>
@@ -2835,55 +2835,55 @@
         <v>22</v>
       </c>
       <c r="AM13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AO13" t="n">
         <v>23</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW13" t="n">
         <v>3</v>
       </c>
       <c r="AX13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AZ13" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BA13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BB13" t="n">
         <v>9</v>
       </c>
       <c r="BC13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -2990,16 +2990,16 @@
         <v>1.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>3</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
         <v>17</v>
@@ -3026,16 +3026,16 @@
         <v>13</v>
       </c>
       <c r="AP14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ14" t="n">
         <v>1</v>
       </c>
       <c r="AR14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT14" t="n">
         <v>30</v>
@@ -3050,23 +3050,23 @@
         <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA14" t="n">
         <v>29</v>
       </c>
       <c r="BB14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC14" t="n">
         <v>13</v>
       </c>
-      <c r="BC14" t="n">
-        <v>12</v>
-      </c>
       <c r="BD14" t="n">
         <v>10</v>
       </c>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
         <v>16</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>19</v>
@@ -3205,13 +3205,13 @@
         <v>3</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>14</v>
@@ -3235,13 +3235,13 @@
         <v>3</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
         <v>6</v>
       </c>
       <c r="BA15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB15" t="n">
         <v>7</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -3354,16 +3354,16 @@
         <v>-1.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG16" t="n">
         <v>17</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>18</v>
       </c>
       <c r="AH16" t="n">
         <v>8</v>
@@ -3375,7 +3375,7 @@
         <v>3</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -3396,7 +3396,7 @@
         <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS16" t="n">
         <v>13</v>
@@ -3405,10 +3405,10 @@
         <v>9</v>
       </c>
       <c r="AU16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
@@ -3417,7 +3417,7 @@
         <v>13</v>
       </c>
       <c r="AY16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ16" t="n">
         <v>5</v>
@@ -3429,7 +3429,7 @@
         <v>26</v>
       </c>
       <c r="BC16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -3458,106 +3458,106 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4</v>
+        <v>0.444</v>
       </c>
       <c r="H17" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I17" t="n">
         <v>40.1</v>
       </c>
       <c r="J17" t="n">
-        <v>83.7</v>
+        <v>84</v>
       </c>
       <c r="K17" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L17" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="M17" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
       <c r="N17" t="n">
         <v>0.358</v>
       </c>
       <c r="O17" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="V17" t="n">
         <v>17.6</v>
       </c>
-      <c r="P17" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.752</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="V17" t="n">
-        <v>17.8</v>
-      </c>
       <c r="W17" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="X17" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AA17" t="n">
         <v>21.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>111</v>
+        <v>111.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.9</v>
+        <v>-1.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AE17" t="n">
         <v>23</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AH17" t="n">
         <v>4</v>
       </c>
       <c r="AI17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL17" t="n">
         <v>12</v>
@@ -3566,52 +3566,52 @@
         <v>12</v>
       </c>
       <c r="AN17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT17" t="n">
         <v>18</v>
       </c>
-      <c r="AO17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>20</v>
-      </c>
       <c r="AU17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV17" t="n">
         <v>29</v>
       </c>
       <c r="AW17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AY17" t="n">
         <v>3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
         <v>8</v>
       </c>
       <c r="BB17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -3718,16 +3718,16 @@
         <v>11.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
         <v>3</v>
       </c>
       <c r="AG18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="n">
         <v>17</v>
@@ -3739,10 +3739,10 @@
         <v>8</v>
       </c>
       <c r="AK18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL18" t="n">
         <v>2</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1</v>
       </c>
       <c r="AM18" t="n">
         <v>4</v>
@@ -3763,16 +3763,16 @@
         <v>12</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU18" t="n">
         <v>6</v>
       </c>
       <c r="AV18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW18" t="n">
         <v>4</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -3900,10 +3900,10 @@
         <v>-10.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF19" t="n">
         <v>27</v>
@@ -3915,13 +3915,13 @@
         <v>8</v>
       </c>
       <c r="AI19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
         <v>25</v>
@@ -3933,7 +3933,7 @@
         <v>28</v>
       </c>
       <c r="AO19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
@@ -3945,22 +3945,22 @@
         <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX19" t="n">
         <v>17</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>17</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -4082,19 +4082,19 @@
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI20" t="n">
         <v>22</v>
@@ -4115,7 +4115,7 @@
         <v>30</v>
       </c>
       <c r="AO20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP20" t="n">
         <v>4</v>
@@ -4127,7 +4127,7 @@
         <v>6</v>
       </c>
       <c r="AS20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT20" t="n">
         <v>4</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -4264,16 +4264,16 @@
         <v>-5.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
         <v>17</v>
@@ -4285,7 +4285,7 @@
         <v>27</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="n">
         <v>29</v>
@@ -4294,19 +4294,19 @@
         <v>30</v>
       </c>
       <c r="AN21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="n">
         <v>26</v>
       </c>
       <c r="AP21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS21" t="n">
         <v>14</v>
@@ -4315,10 +4315,10 @@
         <v>10</v>
       </c>
       <c r="AU21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
         <v>25</v>
@@ -4327,13 +4327,13 @@
         <v>20</v>
       </c>
       <c r="AY21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>-6.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG22" t="n">
         <v>17</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>18</v>
       </c>
       <c r="AH22" t="n">
         <v>17</v>
@@ -4467,13 +4467,13 @@
         <v>26</v>
       </c>
       <c r="AK22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="n">
         <v>18</v>
       </c>
       <c r="AM22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN22" t="n">
         <v>27</v>
@@ -4488,19 +4488,19 @@
         <v>26</v>
       </c>
       <c r="AR22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU22" t="n">
         <v>29</v>
       </c>
       <c r="AV22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW22" t="n">
         <v>28</v>
@@ -4515,7 +4515,7 @@
         <v>7</v>
       </c>
       <c r="BA22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB22" t="n">
         <v>28</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -4628,13 +4628,13 @@
         <v>-4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
         <v>11</v>
       </c>
       <c r="AF23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG23" t="n">
         <v>11</v>
@@ -4646,7 +4646,7 @@
         <v>19</v>
       </c>
       <c r="AJ23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK23" t="n">
         <v>29</v>
@@ -4661,10 +4661,10 @@
         <v>29</v>
       </c>
       <c r="AO23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ23" t="n">
         <v>4</v>
@@ -4673,10 +4673,10 @@
         <v>2</v>
       </c>
       <c r="AS23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU23" t="n">
         <v>30</v>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -4732,85 +4732,85 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="H24" t="n">
         <v>48.4</v>
       </c>
       <c r="I24" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="J24" t="n">
-        <v>88.5</v>
+        <v>89</v>
       </c>
       <c r="K24" t="n">
-        <v>0.477</v>
+        <v>0.473</v>
       </c>
       <c r="L24" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="M24" t="n">
-        <v>34.2</v>
+        <v>34</v>
       </c>
       <c r="N24" t="n">
-        <v>0.366</v>
+        <v>0.358</v>
       </c>
       <c r="O24" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="P24" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.765</v>
+        <v>0.759</v>
       </c>
       <c r="R24" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>37.4</v>
+        <v>38</v>
       </c>
       <c r="T24" t="n">
-        <v>46.8</v>
+        <v>47.8</v>
       </c>
       <c r="U24" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="V24" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="W24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>114.3</v>
+        <v>113.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4822,70 +4822,70 @@
         <v>3</v>
       </c>
       <c r="AH24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI24" t="n">
         <v>8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="n">
         <v>18</v>
       </c>
       <c r="AN24" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AO24" t="n">
         <v>14</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT24" t="n">
         <v>5</v>
       </c>
-      <c r="AT24" t="n">
-        <v>7</v>
-      </c>
       <c r="AU24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>28</v>
       </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AX24" t="n">
         <v>1</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -4992,16 +4992,16 @@
         <v>3.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF25" t="n">
         <v>3</v>
       </c>
       <c r="AG25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH25" t="n">
         <v>8</v>
@@ -5019,16 +5019,16 @@
         <v>8</v>
       </c>
       <c r="AM25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO25" t="n">
         <v>21</v>
       </c>
       <c r="AP25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ25" t="n">
         <v>2</v>
@@ -5037,13 +5037,13 @@
         <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AU25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV25" t="n">
         <v>3</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -5096,160 +5096,160 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
         <v>7</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>0.583</v>
+        <v>0.636</v>
       </c>
       <c r="H26" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>40.5</v>
+        <v>41.3</v>
       </c>
       <c r="J26" t="n">
-        <v>91.3</v>
+        <v>91.7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.443</v>
+        <v>0.45</v>
       </c>
       <c r="L26" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="M26" t="n">
         <v>42.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.383</v>
+        <v>0.391</v>
       </c>
       <c r="O26" t="n">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="P26" t="n">
-        <v>23.1</v>
+        <v>24.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.805</v>
+        <v>0.798</v>
       </c>
       <c r="R26" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="S26" t="n">
-        <v>34.8</v>
+        <v>35.3</v>
       </c>
       <c r="T26" t="n">
         <v>43.8</v>
       </c>
       <c r="U26" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="V26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="W26" t="n">
         <v>8.5</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
         <v>5.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>116</v>
+        <v>118.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE26" t="n">
         <v>5</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AF26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG26" t="n">
         <v>6</v>
       </c>
-      <c r="AF26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>10</v>
-      </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP26" t="n">
         <v>7</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>12</v>
       </c>
       <c r="AQ26" t="n">
         <v>6</v>
       </c>
       <c r="AR26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT26" t="n">
         <v>21</v>
       </c>
       <c r="AU26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV26" t="n">
         <v>2</v>
       </c>
       <c r="AW26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ26" t="n">
         <v>20</v>
       </c>
       <c r="BA26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BC26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -5356,19 +5356,19 @@
         <v>-7.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AI27" t="n">
         <v>12</v>
@@ -5380,13 +5380,13 @@
         <v>12</v>
       </c>
       <c r="AL27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AM27" t="n">
         <v>23</v>
       </c>
       <c r="AN27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO27" t="n">
         <v>2</v>
@@ -5401,10 +5401,10 @@
         <v>13</v>
       </c>
       <c r="AS27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU27" t="n">
         <v>12</v>
@@ -5425,7 +5425,7 @@
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB27" t="n">
         <v>8</v>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -5460,97 +5460,97 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
         <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="H28" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I28" t="n">
         <v>41.9</v>
       </c>
       <c r="J28" t="n">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L28" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="M28" t="n">
         <v>31.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.373</v>
+        <v>0.381</v>
       </c>
       <c r="O28" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="P28" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.784</v>
+        <v>0.787</v>
       </c>
       <c r="R28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="S28" t="n">
-        <v>35.9</v>
+        <v>36.4</v>
       </c>
       <c r="T28" t="n">
-        <v>45.1</v>
+        <v>45.5</v>
       </c>
       <c r="U28" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="V28" t="n">
         <v>10.2</v>
       </c>
       <c r="W28" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y28" t="n">
         <v>6.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>110.7</v>
+        <v>111.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
       </c>
       <c r="AF28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="n">
         <v>9</v>
@@ -5559,25 +5559,25 @@
         <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM28" t="n">
         <v>25</v>
       </c>
       <c r="AN28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>18</v>
@@ -5586,7 +5586,7 @@
         <v>10</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
         <v>11</v>
@@ -5595,10 +5595,10 @@
         <v>1</v>
       </c>
       <c r="AW28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
         <v>26</v>
@@ -5607,13 +5607,13 @@
         <v>4</v>
       </c>
       <c r="BA28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -5642,100 +5642,100 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>8</v>
       </c>
       <c r="G29" t="n">
-        <v>0.273</v>
+        <v>0.2</v>
       </c>
       <c r="H29" t="n">
         <v>48</v>
       </c>
       <c r="I29" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="J29" t="n">
-        <v>89.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L29" t="n">
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="M29" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="O29" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="P29" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="R29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="S29" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="T29" t="n">
         <v>43.5</v>
       </c>
-      <c r="N29" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="O29" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="P29" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.789</v>
-      </c>
-      <c r="R29" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="S29" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>43.2</v>
-      </c>
       <c r="U29" t="n">
-        <v>24.5</v>
+        <v>23.6</v>
       </c>
       <c r="V29" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="W29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X29" t="n">
         <v>6</v>
       </c>
       <c r="Y29" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="AB29" t="n">
         <v>111.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AE29" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF29" t="n">
         <v>27</v>
       </c>
       <c r="AG29" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AH29" t="n">
         <v>17</v>
       </c>
       <c r="AI29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ29" t="n">
         <v>12</v>
@@ -5744,40 +5744,40 @@
         <v>26</v>
       </c>
       <c r="AL29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP29" t="n">
         <v>17</v>
       </c>
-      <c r="AP29" t="n">
-        <v>19</v>
-      </c>
       <c r="AQ29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AR29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS29" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AT29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AV29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX29" t="n">
         <v>6</v>
@@ -5786,16 +5786,16 @@
         <v>30</v>
       </c>
       <c r="AZ29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA29" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -5902,37 +5902,37 @@
         <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF30" t="n">
         <v>3</v>
       </c>
       <c r="AG30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH30" t="n">
         <v>17</v>
       </c>
       <c r="AI30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
         <v>16</v>
       </c>
       <c r="AL30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM30" t="n">
         <v>3</v>
       </c>
       <c r="AN30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO30" t="n">
         <v>29</v>
@@ -5953,10 +5953,10 @@
         <v>1</v>
       </c>
       <c r="AU30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW30" t="n">
         <v>30</v>
@@ -5977,7 +5977,7 @@
         <v>20</v>
       </c>
       <c r="BC30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
@@ -6084,10 +6084,10 @@
         <v>-0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF31" t="n">
         <v>27</v>
@@ -6105,7 +6105,7 @@
         <v>4</v>
       </c>
       <c r="AK31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL31" t="n">
         <v>14</v>
@@ -6114,28 +6114,28 @@
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP31" t="n">
         <v>2</v>
       </c>
       <c r="AQ31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS31" t="n">
         <v>24</v>
       </c>
-      <c r="AR31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>22</v>
-      </c>
       <c r="AT31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AU31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV31" t="n">
         <v>5</v>
@@ -6144,16 +6144,16 @@
         <v>19</v>
       </c>
       <c r="AX31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>30</v>
       </c>
       <c r="BA31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB31" t="n">
         <v>2</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-14-2020-21</t>
+          <t>2021-01-14</t>
         </is>
       </c>
     </row>
